--- a/data/trans_orig/P1428-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1428-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2007</t>
+          <t>Población con diagnóstico de artritis en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>24439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24588</t>
+          <t>24581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47480</t>
+          <t>47294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39254</t>
+          <t>38038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65343</t>
+          <t>66156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248623</t>
+          <t>248571</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263096</t>
+          <t>263353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213358</t>
+          <t>213544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>236250</t>
+          <t>236257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>468505</t>
+          <t>467692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>494594</t>
+          <t>495810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33458</t>
+          <t>32675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76141</t>
+          <t>76864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109313</t>
+          <t>110383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94910</t>
+          <t>94367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136559</t>
+          <t>134715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>459617</t>
+          <t>460400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478444</t>
+          <t>478316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394636</t>
+          <t>393566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>427808</t>
+          <t>427085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>860465</t>
+          <t>862309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>902114</t>
+          <t>902657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19711</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48476</t>
+          <t>46988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75543</t>
+          <t>75281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60278</t>
+          <t>57827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91355</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>299135</t>
+          <t>297513</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312154</t>
+          <t>312109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>259869</t>
+          <t>260131</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286936</t>
+          <t>288424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>562903</t>
+          <t>563825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>593980</t>
+          <t>596431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34366</t>
+          <t>33784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51476</t>
+          <t>51069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80712</t>
+          <t>80484</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72841</t>
+          <t>71954</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108492</t>
+          <t>107906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324305</t>
+          <t>324887</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343590</t>
+          <t>343301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>290744</t>
+          <t>290972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>319980</t>
+          <t>320387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>621635</t>
+          <t>622221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>657286</t>
+          <t>658173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24470</t>
+          <t>25650</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>30986</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44260</t>
+          <t>45111</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75125</t>
+          <t>72696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178838</t>
+          <t>177658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194237</t>
+          <t>193905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>151958</t>
+          <t>152730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176184</t>
+          <t>176682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>335851</t>
+          <t>338280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>366716</t>
+          <t>365865</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35329</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62007</t>
+          <t>61113</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52404</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83081</t>
+          <t>82550</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243712</t>
+          <t>244297</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259770</t>
+          <t>260098</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>216137</t>
+          <t>217031</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>242815</t>
+          <t>243541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>465874</t>
+          <t>466405</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>496551</t>
+          <t>496121</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38402</t>
+          <t>37788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65379</t>
+          <t>65159</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78032</t>
+          <t>77295</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112487</t>
+          <t>112806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123267</t>
+          <t>122582</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168426</t>
+          <t>166449</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>549648</t>
+          <t>549868</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>576625</t>
+          <t>577239</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>525732</t>
+          <t>525413</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>560187</t>
+          <t>560924</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1084820</t>
+          <t>1086797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1129979</t>
+          <t>1130664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64612</t>
+          <t>63811</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96900</t>
+          <t>96348</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>137519</t>
+          <t>139463</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>184664</t>
+          <t>183929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211204</t>
+          <t>211806</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>269227</t>
+          <t>269487</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>646895</t>
+          <t>647447</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>679183</t>
+          <t>679984</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>598847</t>
+          <t>599582</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>645992</t>
+          <t>644048</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1258079</t>
+          <t>1257819</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1316102</t>
+          <t>1315500</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>208322</t>
+          <t>208868</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>266808</t>
+          <t>267097</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>554495</t>
+          <t>552263</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>643555</t>
+          <t>640890</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>775323</t>
+          <t>777516</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>886437</t>
+          <t>889127</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3009735</t>
+          <t>3009446</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3068221</t>
+          <t>3067675</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2735642</t>
+          <t>2738307</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2824702</t>
+          <t>2826934</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5769304</t>
+          <t>5766614</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5880418</t>
+          <t>5878225</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2012</t>
+          <t>Población con diagnóstico de artritis en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>21849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33524</t>
+          <t>34567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>24406</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49822</t>
+          <t>49091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271902</t>
+          <t>272889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288302</t>
+          <t>288104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253721</t>
+          <t>252678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272797</t>
+          <t>273220</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>532161</t>
+          <t>532892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>557368</t>
+          <t>557577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26184</t>
+          <t>26268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35732</t>
+          <t>37325</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64521</t>
+          <t>64625</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48077</t>
+          <t>50151</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81679</t>
+          <t>81927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479343</t>
+          <t>479259</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497338</t>
+          <t>497503</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459244</t>
+          <t>459140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488033</t>
+          <t>486440</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>947613</t>
+          <t>947365</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>981215</t>
+          <t>979141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34811</t>
+          <t>34082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38536</t>
+          <t>37286</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66509</t>
+          <t>64503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>59837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90943</t>
+          <t>92301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289235</t>
+          <t>289964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308702</t>
+          <t>309508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>274511</t>
+          <t>276517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302484</t>
+          <t>303734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>574123</t>
+          <t>572765</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>606749</t>
+          <t>605229</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26293</t>
+          <t>26245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32742</t>
+          <t>33167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58550</t>
+          <t>58363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48108</t>
+          <t>46868</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77371</t>
+          <t>77995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347689</t>
+          <t>347737</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>364215</t>
+          <t>364149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>330401</t>
+          <t>330588</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>356209</t>
+          <t>355784</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>685562</t>
+          <t>684938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>714825</t>
+          <t>716065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46596</t>
+          <t>45830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>34488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59655</t>
+          <t>62308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192743</t>
+          <t>192908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207216</t>
+          <t>207008</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172995</t>
+          <t>173761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195516</t>
+          <t>195607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>372554</t>
+          <t>369901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>398898</t>
+          <t>397721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42679</t>
+          <t>42845</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44573</t>
+          <t>44011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71069</t>
+          <t>70471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72245</t>
+          <t>72562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106816</t>
+          <t>104648</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231302</t>
+          <t>231136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252161</t>
+          <t>251909</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207027</t>
+          <t>207625</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>233523</t>
+          <t>234085</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>445261</t>
+          <t>447429</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>479832</t>
+          <t>479515</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28269</t>
+          <t>27846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53881</t>
+          <t>55152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88555</t>
+          <t>89704</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129752</t>
+          <t>130006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121926</t>
+          <t>126389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172893</t>
+          <t>175291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>608907</t>
+          <t>607636</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>634519</t>
+          <t>634942</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>564101</t>
+          <t>563847</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>605298</t>
+          <t>604149</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1183748</t>
+          <t>1181350</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1234715</t>
+          <t>1230252</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17214</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38541</t>
+          <t>40018</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58312</t>
+          <t>59061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93281</t>
+          <t>94075</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82225</t>
+          <t>80683</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>124207</t>
+          <t>121791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>740557</t>
+          <t>739080</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761884</t>
+          <t>761675</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>729297</t>
+          <t>728503</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>764266</t>
+          <t>763517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1477469</t>
+          <t>1479885</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1519451</t>
+          <t>1520993</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>150414</t>
+          <t>151392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>206132</t>
+          <t>205192</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>401480</t>
+          <t>398302</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>486526</t>
+          <t>480345</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>566335</t>
+          <t>569815</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>662678</t>
+          <t>668340</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3220647</t>
+          <t>3221587</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3276365</t>
+          <t>3275387</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3068572</t>
+          <t>3074753</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3153618</t>
+          <t>3156796</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6319199</t>
+          <t>6313537</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6415542</t>
+          <t>6412062</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2016</t>
+          <t>Población con diagnóstico de artritis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27079</t>
+          <t>25147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16199</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29894</t>
+          <t>30228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57394</t>
+          <t>55907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266682</t>
+          <t>268614</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283502</t>
+          <t>284317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251235</t>
+          <t>252176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272504</t>
+          <t>272824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>525070</t>
+          <t>526557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>552570</t>
+          <t>552236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25463</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35203</t>
+          <t>37203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63289</t>
+          <t>64222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49090</t>
+          <t>49174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81994</t>
+          <t>82842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477112</t>
+          <t>478566</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>493128</t>
+          <t>494029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459795</t>
+          <t>458862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487881</t>
+          <t>485881</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>943665</t>
+          <t>942817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>976569</t>
+          <t>976485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36348</t>
+          <t>36571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28208</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52587</t>
+          <t>51853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297913</t>
+          <t>298384</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>311236</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>299961</t>
+          <t>299738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319785</t>
+          <t>319125</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602287</t>
+          <t>603021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>626666</t>
+          <t>627162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25731</t>
+          <t>24730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37804</t>
+          <t>37711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66153</t>
+          <t>66075</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>51043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81309</t>
+          <t>82732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344233</t>
+          <t>345234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360869</t>
+          <t>361060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>321130</t>
+          <t>321208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349479</t>
+          <t>349572</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>675938</t>
+          <t>674515</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706138</t>
+          <t>706204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>32124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>18577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38912</t>
+          <t>39459</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198080</t>
+          <t>197903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208708</t>
+          <t>208736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186888</t>
+          <t>186463</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205002</t>
+          <t>205090</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390896</t>
+          <t>390349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411285</t>
+          <t>411231</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26490</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>48386</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>35030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61592</t>
+          <t>62918</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244166</t>
+          <t>244488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256933</t>
+          <t>257155</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223064</t>
+          <t>224729</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246625</t>
+          <t>247561</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474646</t>
+          <t>473320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501986</t>
+          <t>501208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35104</t>
+          <t>35001</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41682</t>
+          <t>41198</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73297</t>
+          <t>71951</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62145</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99096</t>
+          <t>99082</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>621454</t>
+          <t>621557</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640584</t>
+          <t>640482</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>617997</t>
+          <t>619343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>649612</t>
+          <t>650096</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1248756</t>
+          <t>1248770</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1285707</t>
+          <t>1285775</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12764</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32036</t>
+          <t>33549</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53075</t>
+          <t>54203</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88418</t>
+          <t>88079</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72363</t>
+          <t>71990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111635</t>
+          <t>112076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>746547</t>
+          <t>745034</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>765819</t>
+          <t>765800</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>737749</t>
+          <t>738088</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>773092</t>
+          <t>771964</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1493115</t>
+          <t>1492674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1532387</t>
+          <t>1532760</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99788</t>
+          <t>101492</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>142343</t>
+          <t>146115</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>294992</t>
+          <t>296250</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>369623</t>
+          <t>370515</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>411559</t>
+          <t>408237</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>500100</t>
+          <t>496976</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3252007</t>
+          <t>3248235</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3294562</t>
+          <t>3292858</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3174919</t>
+          <t>3174027</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3249550</t>
+          <t>3248292</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6438792</t>
+          <t>6441916</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6527333</t>
+          <t>6530655</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2023</t>
+          <t>Población con diagnóstico de artritis en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>31214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24519</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41762</t>
+          <t>41326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295540</t>
+          <t>294985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>306590</t>
+          <t>306509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259592</t>
+          <t>258421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273112</t>
+          <t>272189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559315</t>
+          <t>559751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576558</t>
+          <t>576348</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31065</t>
+          <t>31624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36647</t>
+          <t>37764</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>58079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54657</t>
+          <t>53689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82273</t>
+          <t>80947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485496</t>
+          <t>484937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504125</t>
+          <t>504061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449312</t>
+          <t>448665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470097</t>
+          <t>468980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>941032</t>
+          <t>942358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>968648</t>
+          <t>969616</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45110</t>
+          <t>45062</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65679</t>
+          <t>67872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>61584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89424</t>
+          <t>88470</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288725</t>
+          <t>288038</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302914</t>
+          <t>303083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282897</t>
+          <t>280704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303466</t>
+          <t>303514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>575202</t>
+          <t>576156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>600703</t>
+          <t>603042</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41567</t>
+          <t>40580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53202</t>
+          <t>54087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113154</t>
+          <t>113183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87518</t>
+          <t>82133</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140614</t>
+          <t>138840</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270990</t>
+          <t>271977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>292127</t>
+          <t>292707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362158</t>
+          <t>362129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>422110</t>
+          <t>421225</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>647255</t>
+          <t>649029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>700351</t>
+          <t>705736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31834</t>
+          <t>32322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45593</t>
+          <t>46304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40793</t>
+          <t>40040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57912</t>
+          <t>56679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163614</t>
+          <t>163907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172474</t>
+          <t>172789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162248</t>
+          <t>161537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176007</t>
+          <t>175519</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>328671</t>
+          <t>329904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>345790</t>
+          <t>346543</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30720</t>
+          <t>30808</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40187</t>
+          <t>39526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57998</t>
+          <t>57010</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60323</t>
+          <t>60573</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82798</t>
+          <t>83397</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238916</t>
+          <t>238828</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252054</t>
+          <t>252689</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>198389</t>
+          <t>199377</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>216200</t>
+          <t>216861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>443225</t>
+          <t>442626</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>465700</t>
+          <t>465450</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>53777</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124679</t>
+          <t>125775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>565503</t>
+          <t>576148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>155637</t>
+          <t>158146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>753170</t>
+          <t>751927</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>563837</t>
+          <t>564449</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>587979</t>
+          <t>588238</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>280222</t>
+          <t>269577</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>721046</t>
+          <t>719950</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>710781</t>
+          <t>712024</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1308314</t>
+          <t>1305805</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>79584</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>111433</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69782</t>
+          <t>72426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143478</t>
+          <t>145213</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>894528</t>
+          <t>894121</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>920452</t>
+          <t>919864</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>601625</t>
+          <t>603959</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>635389</t>
+          <t>635808</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1500634</t>
+          <t>1498899</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1574330</t>
+          <t>1571686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>138106</t>
+          <t>136351</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>199119</t>
+          <t>202713</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>510725</t>
+          <t>508592</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1273082</t>
+          <t>1323440</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>663265</t>
+          <t>661515</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1509503</t>
+          <t>1704021</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3252815</t>
+          <t>3249221</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3313828</t>
+          <t>3315583</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2372529</t>
+          <t>2322171</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3134886</t>
+          <t>3137019</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5588043</t>
+          <t>5393525</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6434281</t>
+          <t>6436031</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1428-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1428-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24439</t>
+          <t>24918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24581</t>
+          <t>24554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47294</t>
+          <t>46467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38038</t>
+          <t>37660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66156</t>
+          <t>64879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248571</t>
+          <t>248092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263353</t>
+          <t>263101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213544</t>
+          <t>214371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>236257</t>
+          <t>236284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>467692</t>
+          <t>468969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>495810</t>
+          <t>496188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32675</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76864</t>
+          <t>74917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110383</t>
+          <t>111186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94367</t>
+          <t>97159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134715</t>
+          <t>137883</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460400</t>
+          <t>457971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478316</t>
+          <t>477943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>393566</t>
+          <t>392763</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>427085</t>
+          <t>429032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862309</t>
+          <t>859141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>902657</t>
+          <t>899865</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46988</t>
+          <t>47881</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75281</t>
+          <t>76773</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57827</t>
+          <t>59286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90433</t>
+          <t>92922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297513</t>
+          <t>299468</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312109</t>
+          <t>312183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260131</t>
+          <t>258639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288424</t>
+          <t>287531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>563825</t>
+          <t>561336</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>596431</t>
+          <t>594972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>34931</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>50744</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80484</t>
+          <t>77551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71954</t>
+          <t>71284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107906</t>
+          <t>106197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324887</t>
+          <t>323740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343301</t>
+          <t>342915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>290972</t>
+          <t>293905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>320387</t>
+          <t>320712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>622221</t>
+          <t>623930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>658173</t>
+          <t>658843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25650</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30986</t>
+          <t>31148</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54938</t>
+          <t>55619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45111</t>
+          <t>43220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72696</t>
+          <t>73250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177658</t>
+          <t>178700</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193905</t>
+          <t>194275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152730</t>
+          <t>152049</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176682</t>
+          <t>176520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>338280</t>
+          <t>337726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365865</t>
+          <t>367756</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26514</t>
+          <t>27829</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34603</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61113</t>
+          <t>61987</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>51988</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82550</t>
+          <t>81521</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244297</t>
+          <t>242982</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260098</t>
+          <t>259635</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217031</t>
+          <t>216157</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243541</t>
+          <t>241687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>466405</t>
+          <t>467434</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>496121</t>
+          <t>496967</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37788</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65159</t>
+          <t>65177</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77295</t>
+          <t>75719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112806</t>
+          <t>110320</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122582</t>
+          <t>122691</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166449</t>
+          <t>168657</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>549868</t>
+          <t>549850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>577239</t>
+          <t>577959</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>525413</t>
+          <t>527899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>560924</t>
+          <t>562500</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1086797</t>
+          <t>1084589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1130664</t>
+          <t>1130555</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63811</t>
+          <t>63025</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96348</t>
+          <t>96368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>139463</t>
+          <t>139530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>183929</t>
+          <t>182836</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211806</t>
+          <t>212843</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>269487</t>
+          <t>266936</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>647447</t>
+          <t>647427</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>679984</t>
+          <t>680770</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>599582</t>
+          <t>600675</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>644048</t>
+          <t>643981</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1257819</t>
+          <t>1260370</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1315500</t>
+          <t>1314463</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>208868</t>
+          <t>211644</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>267097</t>
+          <t>267642</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>552263</t>
+          <t>553969</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>640890</t>
+          <t>642144</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>777516</t>
+          <t>778081</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>889127</t>
+          <t>889635</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3009446</t>
+          <t>3008901</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3067675</t>
+          <t>3064899</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2738307</t>
+          <t>2737053</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2826934</t>
+          <t>2825228</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5766614</t>
+          <t>5766106</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5878225</t>
+          <t>5877660</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21849</t>
+          <t>22723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>34461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24406</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49091</t>
+          <t>49724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>272889</t>
+          <t>272015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288104</t>
+          <t>288025</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252678</t>
+          <t>252784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273220</t>
+          <t>272674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>532892</t>
+          <t>532259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>557577</t>
+          <t>557825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26268</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37325</t>
+          <t>37352</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64625</t>
+          <t>63169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50151</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81927</t>
+          <t>81232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479259</t>
+          <t>479878</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497503</t>
+          <t>497320</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459140</t>
+          <t>460596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486440</t>
+          <t>486413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>947365</t>
+          <t>948060</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>979141</t>
+          <t>980316</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34082</t>
+          <t>33268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37286</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64503</t>
+          <t>65017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59837</t>
+          <t>58213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92301</t>
+          <t>91146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289964</t>
+          <t>290778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309508</t>
+          <t>309053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276517</t>
+          <t>276003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303734</t>
+          <t>302649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>572765</t>
+          <t>573920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>605229</t>
+          <t>606853</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26245</t>
+          <t>26918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33167</t>
+          <t>32733</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58363</t>
+          <t>58041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46868</t>
+          <t>49828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77995</t>
+          <t>78956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347737</t>
+          <t>347064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>364149</t>
+          <t>364200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>330588</t>
+          <t>330910</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>355784</t>
+          <t>356218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>684938</t>
+          <t>683977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716065</t>
+          <t>713105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>46485</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34488</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62308</t>
+          <t>58770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192908</t>
+          <t>193309</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207008</t>
+          <t>207207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173761</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195607</t>
+          <t>194601</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369901</t>
+          <t>373439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>397721</t>
+          <t>399149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42845</t>
+          <t>41503</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44011</t>
+          <t>44111</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70471</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72562</t>
+          <t>72252</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104648</t>
+          <t>104201</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231136</t>
+          <t>232478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251909</t>
+          <t>253448</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207625</t>
+          <t>207157</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>234085</t>
+          <t>233985</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>447429</t>
+          <t>447876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>479515</t>
+          <t>479825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,91%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27846</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55152</t>
+          <t>56145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89704</t>
+          <t>88381</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130006</t>
+          <t>126934</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126389</t>
+          <t>126005</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>175291</t>
+          <t>174142</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>607636</t>
+          <t>606643</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>634942</t>
+          <t>634449</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>563847</t>
+          <t>566919</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>604149</t>
+          <t>605472</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1181350</t>
+          <t>1182499</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1230252</t>
+          <t>1230636</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40018</t>
+          <t>38574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59061</t>
+          <t>58171</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94075</t>
+          <t>93519</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>80683</t>
+          <t>81292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121791</t>
+          <t>122069</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>739080</t>
+          <t>740524</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761675</t>
+          <t>762266</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>728503</t>
+          <t>729059</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>763517</t>
+          <t>764407</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1479885</t>
+          <t>1479607</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1520993</t>
+          <t>1520384</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>151392</t>
+          <t>150975</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>205192</t>
+          <t>206819</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>398302</t>
+          <t>401719</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>480345</t>
+          <t>481574</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>569815</t>
+          <t>572809</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>668340</t>
+          <t>671632</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3221587</t>
+          <t>3219960</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3275387</t>
+          <t>3275804</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3074753</t>
+          <t>3073524</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3156796</t>
+          <t>3153379</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6313537</t>
+          <t>6310245</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6412062</t>
+          <t>6409068</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25147</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36527</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30228</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55907</t>
+          <t>58017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268614</t>
+          <t>267314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284317</t>
+          <t>284239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252176</t>
+          <t>250625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272824</t>
+          <t>272138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526557</t>
+          <t>524447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>552236</t>
+          <t>552008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24009</t>
+          <t>24769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,82 +7737,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>48660</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>36329</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>62361</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>64046</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>49033</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>82440</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>48660</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>37203</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>64222</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>64046</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>49174</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>82842</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>478566</t>
+          <t>477806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494029</t>
+          <t>493733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,82 +7850,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>95,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>474424</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>460723</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>486755</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>88,08%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>93,05%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>961613</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>943219</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>976626</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>93,76%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>95,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>474424</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>458862</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>485881</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>92,89%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>961613</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>942817</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>976485</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>93,76%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>91,92%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>16851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>37240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27712</t>
+          <t>26938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>50687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298384</t>
+          <t>298595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311236</t>
+          <t>312054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>299738</t>
+          <t>299069</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319125</t>
+          <t>319458</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>603021</t>
+          <t>604187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627162</t>
+          <t>627936</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>25132</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37711</t>
+          <t>37423</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66075</t>
+          <t>66664</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51043</t>
+          <t>50330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82732</t>
+          <t>82176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345234</t>
+          <t>344832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361060</t>
+          <t>361066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>321208</t>
+          <t>320619</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349572</t>
+          <t>349860</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674515</t>
+          <t>675071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706204</t>
+          <t>706917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32124</t>
+          <t>31808</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>18518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39459</t>
+          <t>38895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197903</t>
+          <t>198112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208736</t>
+          <t>208516</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186463</t>
+          <t>186779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205090</t>
+          <t>205208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390349</t>
+          <t>390913</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411231</t>
+          <t>411290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>25607</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48386</t>
+          <t>49165</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35030</t>
+          <t>34409</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62918</t>
+          <t>61485</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244488</t>
+          <t>243567</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257155</t>
+          <t>256957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224729</t>
+          <t>223950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247561</t>
+          <t>247508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>473320</t>
+          <t>474753</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501208</t>
+          <t>501829</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35001</t>
+          <t>35038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41198</t>
+          <t>41008</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71951</t>
+          <t>70681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62077</t>
+          <t>62812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>100305</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>621557</t>
+          <t>621520</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640482</t>
+          <t>640965</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>619343</t>
+          <t>620613</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>650096</t>
+          <t>650286</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1248770</t>
+          <t>1247547</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1285775</t>
+          <t>1285040</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33549</t>
+          <t>32818</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54203</t>
+          <t>53418</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88079</t>
+          <t>89438</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71990</t>
+          <t>71320</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112076</t>
+          <t>109733</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>745034</t>
+          <t>745765</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>765800</t>
+          <t>766462</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>738088</t>
+          <t>736729</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>771964</t>
+          <t>772749</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1492674</t>
+          <t>1495017</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1532760</t>
+          <t>1533430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>101492</t>
+          <t>100603</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>146115</t>
+          <t>145592</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>296250</t>
+          <t>298270</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>370515</t>
+          <t>371859</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>408237</t>
+          <t>412329</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>496976</t>
+          <t>494081</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3248235</t>
+          <t>3248758</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3292858</t>
+          <t>3293747</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3174027</t>
+          <t>3172683</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3248292</t>
+          <t>3246272</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6441916</t>
+          <t>6444811</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6530655</t>
+          <t>6526563</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -10697,102 +10697,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>24306</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17874</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31345</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>33544</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>25049</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>42210</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>22882</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17446</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>31214</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>32079</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>24729</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>41326</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -10810,102 +10810,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>302246</t>
+          <t>309607</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>294985</t>
+          <t>303462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>306509</t>
+          <t>314374</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>291755</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>284716</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>298187</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>92,31%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>601362</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>592696</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>609857</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>94,72%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>266753</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>258421</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>272189</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,1%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>89,22%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>568998</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>559751</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>576348</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31624</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46549</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37764</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58079</t>
+          <t>59679</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>66484</t>
+          <t>68775</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53689</t>
+          <t>54943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80947</t>
+          <t>84010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>496625</t>
+          <t>508397</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484937</t>
+          <t>498287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504061</t>
+          <t>515836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>460195</t>
+          <t>489239</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448665</t>
+          <t>477989</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>468980</t>
+          <t>499187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>956821</t>
+          <t>997636</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>942358</t>
+          <t>982401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>969616</t>
+          <t>1011468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516561</t>
+          <t>528743</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516561</t>
+          <t>528743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516561</t>
+          <t>528743</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>506744</t>
+          <t>537668</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>506744</t>
+          <t>537668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>506744</t>
+          <t>537668</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1023305</t>
+          <t>1066411</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1023305</t>
+          <t>1066411</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1023305</t>
+          <t>1066411</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>18920</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55629</t>
+          <t>56605</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45062</t>
+          <t>45717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67872</t>
+          <t>67098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>75121</t>
+          <t>75525</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61584</t>
+          <t>64715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88470</t>
+          <t>89480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>296558</t>
+          <t>297073</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288038</t>
+          <t>288724</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>303083</t>
+          <t>303002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>292947</t>
+          <t>299219</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>280704</t>
+          <t>288726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303514</t>
+          <t>310107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>589505</t>
+          <t>596293</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>576156</t>
+          <t>582338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>603042</t>
+          <t>607103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>355824</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>355824</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>355824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664626</t>
+          <t>671818</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664626</t>
+          <t>671818</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664626</t>
+          <t>671818</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>31640</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19850</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40580</t>
+          <t>43873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88008</t>
+          <t>94515</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54087</t>
+          <t>81158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113183</t>
+          <t>110499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>116856</t>
+          <t>126156</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82133</t>
+          <t>109191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138840</t>
+          <t>144862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>283710</t>
+          <t>341505</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271977</t>
+          <t>329272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>292707</t>
+          <t>350550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>387304</t>
+          <t>326990</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362129</t>
+          <t>311006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>421225</t>
+          <t>340347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>671013</t>
+          <t>668495</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>649029</t>
+          <t>649789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>705736</t>
+          <t>685460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475312</t>
+          <t>421505</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475312</t>
+          <t>421505</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475312</t>
+          <t>421505</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787869</t>
+          <t>794651</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787869</t>
+          <t>794651</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787869</t>
+          <t>794651</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>40400</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>33529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46304</t>
+          <t>47980</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>48354</t>
+          <t>51270</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40040</t>
+          <t>42623</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56679</t>
+          <t>61597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>169015</t>
+          <t>194794</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163907</t>
+          <t>188948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172789</t>
+          <t>198661</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>169214</t>
+          <t>185968</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>161537</t>
+          <t>178388</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175519</t>
+          <t>192839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>338229</t>
+          <t>380763</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>329904</t>
+          <t>370436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>346543</t>
+          <t>389410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207841</t>
+          <t>226368</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207841</t>
+          <t>226368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207841</t>
+          <t>226368</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386583</t>
+          <t>432033</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386583</t>
+          <t>432033</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386583</t>
+          <t>432033</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23172</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>16927</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30808</t>
+          <t>31240</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48038</t>
+          <t>48826</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39526</t>
+          <t>39871</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57010</t>
+          <t>57605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>71210</t>
+          <t>71587</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60573</t>
+          <t>61703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83397</t>
+          <t>83728</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>246464</t>
+          <t>247946</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238828</t>
+          <t>239467</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252689</t>
+          <t>253780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>208349</t>
+          <t>214273</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>199377</t>
+          <t>205494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>216861</t>
+          <t>223228</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>454813</t>
+          <t>462219</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>442626</t>
+          <t>450078</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>465450</t>
+          <t>472103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41072</t>
+          <t>45783</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>33840</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53777</t>
+          <t>59219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>304615</t>
+          <t>121326</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125775</t>
+          <t>104346</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>576148</t>
+          <t>141163</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>345687</t>
+          <t>167108</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>158146</t>
+          <t>144834</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>751927</t>
+          <t>189931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>577154</t>
+          <t>667436</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>564449</t>
+          <t>654000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>588238</t>
+          <t>679379</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>541110</t>
+          <t>645850</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>269577</t>
+          <t>626013</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>719950</t>
+          <t>662830</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1118264</t>
+          <t>1313287</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>712024</t>
+          <t>1290464</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1305805</t>
+          <t>1335561</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>618226</t>
+          <t>713219</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>618226</t>
+          <t>713219</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>618226</t>
+          <t>713219</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>845725</t>
+          <t>767176</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>845725</t>
+          <t>767176</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>845725</t>
+          <t>767176</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1463951</t>
+          <t>1480395</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1463951</t>
+          <t>1480395</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1463951</t>
+          <t>1480395</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>25549</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34599</t>
+          <t>36365</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>92844</t>
+          <t>100360</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79584</t>
+          <t>86231</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111433</t>
+          <t>117076</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>114965</t>
+          <t>125909</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72426</t>
+          <t>109873</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145213</t>
+          <t>145356</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>906599</t>
+          <t>772523</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>894121</t>
+          <t>761707</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>919864</t>
+          <t>779651</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>622548</t>
+          <t>730249</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>603959</t>
+          <t>713533</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>635808</t>
+          <t>744378</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1529147</t>
+          <t>1502772</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1498899</t>
+          <t>1483325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1571686</t>
+          <t>1518808</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>185107</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>160410</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>202713</t>
+          <t>210735</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>697191</t>
+          <t>534768</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>508592</t>
+          <t>500818</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1323440</t>
+          <t>566276</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>870755</t>
+          <t>719874</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>661515</t>
+          <t>673935</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1704021</t>
+          <t>757593</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3278370</t>
+          <t>3339283</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3249221</t>
+          <t>3313655</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3315583</t>
+          <t>3363980</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2948420</t>
+          <t>3183542</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2322171</t>
+          <t>3152034</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3137019</t>
+          <t>3217492</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6226791</t>
+          <t>6522826</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5393525</t>
+          <t>6485107</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6436031</t>
+          <t>6568765</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3451934</t>
+          <t>3524390</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3451934</t>
+          <t>3524390</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3451934</t>
+          <t>3524390</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3645611</t>
+          <t>3718310</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3645611</t>
+          <t>3718310</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3645611</t>
+          <t>3718310</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7097546</t>
+          <t>7242700</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7097546</t>
+          <t>7242700</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7097546</t>
+          <t>7242700</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
